--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2197,13 +2197,17 @@
         <v>40</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:19</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2059,13 +2059,17 @@
         <v>20</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:19</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2109,13 +2109,17 @@
         <v>30</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-13 01:21</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1617,13 +1617,17 @@
         <v>20</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-13 18:16</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2351,13 +2351,17 @@
         <v>30</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-14 03:44</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2493,13 +2493,17 @@
         <v>30</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-14 10:41</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2305,13 +2305,17 @@
         <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-14 10:55</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2451,13 +2451,17 @@
         <v>20</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:38</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2597,13 +2597,17 @@
         <v>40</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:40</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1967,13 +1967,17 @@
         <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:34</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2263,13 +2263,17 @@
         <v>30</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:06</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2701,13 +2701,17 @@
         <v>20</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:59</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2167,13 +2167,17 @@
         <v>20</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-16 03:20</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2755,13 +2755,17 @@
         <v>30</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:58</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2659,13 +2659,17 @@
         <v>40</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:43</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1920,14 +1920,10 @@
         <v>30</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:14</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1966,14 +1966,10 @@
         <v>20</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-09-15 01:34</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2012,14 +2012,10 @@
         <v>45</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:44</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2058,14 +2058,10 @@
         <v>20</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:19</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1920,10 +1920,14 @@
         <v>30</v>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:45</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1966,10 +1970,14 @@
         <v>20</v>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:45</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2012,10 +2020,14 @@
         <v>45</v>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:45</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2070,10 +2070,14 @@
         <v>20</v>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:45</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2417,13 +2417,17 @@
         <v>20</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:46</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2813,13 +2813,17 @@
         <v>20</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:13</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1937"/>
+  <dimension ref="A1:L1938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89778,6 +89778,52 @@
       </c>
       <c r="K1937" t="inlineStr"/>
       <c r="L1937" t="inlineStr"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="n">
+        <v>3862</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>English Life - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>English Live</t>
+        </is>
+      </c>
+      <c r="H1938" t="n">
+        <v>45</v>
+      </c>
+      <c r="I1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1938" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1938" t="inlineStr"/>
+      <c r="L1938" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -89817,13 +89817,17 @@
         <v>45</v>
       </c>
       <c r="I1938" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J1938" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1938" t="inlineStr"/>
-      <c r="L1938" t="inlineStr"/>
+      <c r="L1938" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2567,13 +2567,17 @@
         <v>20</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:18</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3235,13 +3235,17 @@
         <v>30</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:19</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14942,7 +14942,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -20278,7 +20278,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21336,7 +21336,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -21658,7 +21658,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -21704,7 +21704,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -22072,7 +22072,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -22256,7 +22256,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -22394,7 +22394,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22808,7 +22808,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -23084,7 +23084,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -23268,7 +23268,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -24510,7 +24510,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -24786,7 +24786,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -24878,7 +24878,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -24970,7 +24970,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -25200,7 +25200,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -25660,7 +25660,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -25890,7 +25890,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -25936,7 +25936,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -26028,7 +26028,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -26442,7 +26442,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -26948,7 +26948,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -27178,7 +27178,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -27362,7 +27362,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -27500,7 +27500,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -27592,7 +27592,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -27822,7 +27822,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -28052,7 +28052,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -28098,7 +28098,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -28236,7 +28236,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -28374,7 +28374,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -28650,7 +28650,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -28742,7 +28742,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -28880,7 +28880,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -29110,7 +29110,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -29294,7 +29294,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2867,13 +2867,17 @@
         <v>30</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:34</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2917,13 +2917,17 @@
         <v>20</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:20</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2967,13 +2967,17 @@
         <v>20</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:35</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3017,13 +3017,17 @@
         <v>20</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:55</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3067,13 +3067,17 @@
         <v>45</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:38</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3117,13 +3117,17 @@
         <v>30</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:19</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3213,13 +3213,17 @@
         <v>20</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:19</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3313,13 +3313,17 @@
         <v>20</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-26 02:45</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3167,13 +3167,17 @@
         <v>20</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:36</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3459,13 +3459,17 @@
         <v>20</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:36</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -4199,13 +4199,17 @@
         <v>30</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-29 18:36</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -18804,7 +18804,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -19632,7 +19632,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -21150,7 +21150,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -22668,7 +22668,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22806,7 +22806,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -23450,7 +23450,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -24462,7 +24462,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -24830,7 +24830,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -24922,7 +24922,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -24968,7 +24968,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -25244,7 +25244,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -25290,7 +25290,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -25382,7 +25382,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -25520,7 +25520,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -25612,7 +25612,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -25888,7 +25888,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -26026,7 +26026,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -26394,7 +26394,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -26624,7 +26624,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -26808,7 +26808,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -27222,7 +27222,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -27268,7 +27268,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -27406,7 +27406,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -27498,7 +27498,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -28142,7 +28142,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -28188,7 +28188,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -28418,7 +28418,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -28464,7 +28464,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -28510,7 +28510,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -28694,7 +28694,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -28786,7 +28786,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -28970,7 +28970,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -29062,7 +29062,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -29292,7 +29292,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -29338,7 +29338,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -63975,13 +63975,17 @@
         <v>30</v>
       </c>
       <c r="I1375" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1375" t="inlineStr"/>
-      <c r="L1375" t="inlineStr"/>
+      <c r="L1375" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:30</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -63929,13 +63929,17 @@
         <v>40</v>
       </c>
       <c r="I1374" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1374" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1374" t="inlineStr"/>
-      <c r="L1374" t="inlineStr"/>
+      <c r="L1374" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:34</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -64012,7 +64012,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>English Live - Exercício de gramática</t>
+          <t>Hyperlingua - Exercício de gramática</t>
         </is>
       </c>
       <c r="F1376" t="inlineStr">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -64029,13 +64029,17 @@
         <v>30</v>
       </c>
       <c r="I1376" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1376" t="inlineStr"/>
-      <c r="L1376" t="inlineStr"/>
+      <c r="L1376" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:09</t>
+        </is>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1871"/>
+  <dimension ref="A1:L1872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86810,6 +86810,52 @@
       </c>
       <c r="K1871" t="inlineStr"/>
       <c r="L1871" t="inlineStr"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="n">
+        <v>4361</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duolingo - Tarefas de Hoje </t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1872" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1872" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1872" t="inlineStr"/>
+      <c r="L1872" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
